--- a/users.xlsx
+++ b/users.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U343147\Desktop\FamilyOS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U343147\Desktop\FamilyOS_Beta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{275EC663-F5ED-43AC-8CE5-4DB24DF60378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD42DD4-5270-44ED-A018-5096E406F19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
   <si>
     <t>Username</t>
   </si>
@@ -68,6 +68,9 @@
   </si>
   <si>
     <t>Aria</t>
+  </si>
+  <si>
+    <t>Mirren</t>
   </si>
 </sst>
 </file>
@@ -407,7 +410,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.36328125" bestFit="1" customWidth="1"/>
@@ -498,6 +501,20 @@
       </c>
       <c r="D6" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
